--- a/research/traditional_assets/database/data/switzerland/switzerland_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_semiconductor_equip.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.327</v>
+        <v>-0.294</v>
       </c>
       <c r="G2">
-        <v>-0.5619967793880838</v>
+        <v>-0.8995145631067961</v>
       </c>
       <c r="H2">
-        <v>-1.017713365539453</v>
+        <v>-0.9635922330097088</v>
       </c>
       <c r="I2">
-        <v>-1.172253976870436</v>
+        <v>-0.9830375895804702</v>
       </c>
       <c r="J2">
-        <v>-1.172253976870436</v>
+        <v>-0.9830375895804702</v>
       </c>
       <c r="K2">
-        <v>-69.59999999999999</v>
+        <v>-109.2</v>
       </c>
       <c r="L2">
-        <v>-1.120772946859903</v>
+        <v>-1.325242718446602</v>
       </c>
       <c r="M2">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.001897983392645314</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.03218390804597702</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>2.24</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>71.90000000000001</v>
+        <v>175</v>
       </c>
       <c r="V2">
-        <v>0.0609218776478563</v>
+        <v>0.08443093549476528</v>
       </c>
       <c r="W2">
-        <v>-0.4826629680998613</v>
+        <v>-0.4488286066584464</v>
       </c>
       <c r="X2">
-        <v>0.09376736415657412</v>
+        <v>0.1688902432958835</v>
       </c>
       <c r="Y2">
-        <v>-0.5764303322564355</v>
+        <v>-0.6177188499543299</v>
       </c>
       <c r="Z2">
-        <v>0.3899899812821939</v>
+        <v>0.4202355945750855</v>
       </c>
       <c r="AA2">
-        <v>-0.4571673064976786</v>
+        <v>-0.4131073859470078</v>
       </c>
       <c r="AB2">
-        <v>0.09239581571097759</v>
+        <v>0.1544546354399836</v>
       </c>
       <c r="AC2">
-        <v>-0.5495631222086562</v>
+        <v>-0.5675620213869914</v>
       </c>
       <c r="AD2">
-        <v>0.059</v>
+        <v>243.4</v>
       </c>
       <c r="AE2">
-        <v>23.5348598182703</v>
+        <v>30.21148690715371</v>
       </c>
       <c r="AF2">
-        <v>23.5938598182703</v>
+        <v>273.6114869071537</v>
       </c>
       <c r="AG2">
-        <v>-48.3061401817297</v>
+        <v>98.61148690715373</v>
       </c>
       <c r="AH2">
-        <v>0.01959958478425212</v>
+        <v>0.1166134541104008</v>
       </c>
       <c r="AI2">
-        <v>0.08840165837586338</v>
+        <v>0.5428675615830894</v>
       </c>
       <c r="AJ2">
-        <v>-0.04267727027822682</v>
+        <v>0.04541563359369379</v>
       </c>
       <c r="AK2">
-        <v>-0.2477315964038554</v>
+        <v>0.2997204986188876</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="AM2">
-        <v>-3.93</v>
+        <v>16.3</v>
       </c>
       <c r="AN2">
-        <v>-0.0009951087873165795</v>
+        <v>-3.941062176165803</v>
+      </c>
+      <c r="AO2">
+        <v>-4.993865030674847</v>
       </c>
       <c r="AP2">
-        <v>0.8147434673929786</v>
+        <v>-1.59668858334122</v>
       </c>
       <c r="AQ2">
-        <v>18.42239185750636</v>
+        <v>-4.993865030674847</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.327</v>
+        <v>-0.294</v>
       </c>
       <c r="G3">
-        <v>-0.5619967793880838</v>
+        <v>-0.8995145631067961</v>
       </c>
       <c r="H3">
-        <v>-1.017713365539453</v>
+        <v>-0.9635922330097088</v>
       </c>
       <c r="I3">
-        <v>-1.172253976870436</v>
+        <v>-0.9830375895804702</v>
       </c>
       <c r="J3">
-        <v>-1.172253976870436</v>
+        <v>-0.9830375895804702</v>
       </c>
       <c r="K3">
-        <v>-69.59999999999999</v>
+        <v>-109.2</v>
       </c>
       <c r="L3">
-        <v>-1.120772946859903</v>
+        <v>-1.325242718446602</v>
       </c>
       <c r="M3">
-        <v>2.24</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.001897983392645314</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.03218390804597702</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,76 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2.24</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>71.90000000000001</v>
+        <v>175</v>
       </c>
       <c r="V3">
-        <v>0.0609218776478563</v>
+        <v>0.08443093549476528</v>
       </c>
       <c r="W3">
-        <v>-0.4826629680998613</v>
+        <v>-0.4488286066584464</v>
       </c>
       <c r="X3">
-        <v>0.09376736415657412</v>
+        <v>0.1688902432958835</v>
       </c>
       <c r="Y3">
-        <v>-0.5764303322564355</v>
+        <v>-0.6177188499543299</v>
       </c>
       <c r="Z3">
-        <v>0.3899899812821939</v>
+        <v>0.4202355945750855</v>
       </c>
       <c r="AA3">
-        <v>-0.4571673064976786</v>
+        <v>-0.4131073859470078</v>
       </c>
       <c r="AB3">
-        <v>0.09239581571097759</v>
+        <v>0.1544546354399836</v>
       </c>
       <c r="AC3">
-        <v>-0.5495631222086562</v>
+        <v>-0.5675620213869914</v>
       </c>
       <c r="AD3">
-        <v>0.059</v>
+        <v>243.4</v>
       </c>
       <c r="AE3">
-        <v>23.5348598182703</v>
+        <v>30.21148690715371</v>
       </c>
       <c r="AF3">
-        <v>23.5938598182703</v>
+        <v>273.6114869071537</v>
       </c>
       <c r="AG3">
-        <v>-48.3061401817297</v>
+        <v>98.61148690715373</v>
       </c>
       <c r="AH3">
-        <v>0.01959958478425212</v>
+        <v>0.1166134541104008</v>
       </c>
       <c r="AI3">
-        <v>0.08840165837586338</v>
+        <v>0.5428675615830894</v>
       </c>
       <c r="AJ3">
-        <v>-0.04267727027822682</v>
+        <v>0.04541563359369379</v>
       </c>
       <c r="AK3">
-        <v>-0.2477315964038554</v>
+        <v>0.2997204986188876</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="AM3">
-        <v>-3.93</v>
+        <v>16.3</v>
       </c>
       <c r="AN3">
-        <v>-0.0009951087873165795</v>
+        <v>-3.941062176165803</v>
+      </c>
+      <c r="AO3">
+        <v>-4.993865030674847</v>
       </c>
       <c r="AP3">
-        <v>0.8147434673929786</v>
+        <v>-1.59668858334122</v>
       </c>
       <c r="AQ3">
-        <v>18.42239185750636</v>
+        <v>-4.993865030674847</v>
       </c>
     </row>
   </sheetData>
